--- a/Assets/Data/StageSymbol10.xlsx
+++ b/Assets/Data/StageSymbol10.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070"/>
+    <workbookView windowWidth="19200" windowHeight="6620"/>
   </bookViews>
   <sheets>
     <sheet name="StageSymbols" sheetId="1" r:id="rId1"/>
@@ -75,9 +75,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -97,14 +97,105 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -118,40 +209,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -170,68 +232,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -242,25 +242,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -272,157 +416,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -451,30 +451,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -486,26 +462,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -528,8 +484,52 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -541,16 +541,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -559,127 +559,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/StageSymbol10.xlsx
+++ b/Assets/Data/StageSymbol10.xlsx
@@ -55,9 +55,6 @@
     <t>バトル</t>
   </si>
   <si>
-    <t>リソース</t>
-  </si>
-  <si>
     <t>魔法入手</t>
   </si>
   <si>
@@ -69,16 +66,19 @@
   <si>
     <t>ボス戦</t>
   </si>
+  <si>
+    <t>リソース</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -97,14 +97,30 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -118,6 +134,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -126,50 +170,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -194,13 +194,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -217,6 +210,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -248,25 +248,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -285,144 +423,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -541,58 +541,58 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -601,85 +601,85 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1285,11 +1285,11 @@
         <v>0</v>
       </c>
       <c r="D5" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E5" s="1" t="str">
         <f>INDEX([1]Define!J:J,MATCH(D5,[1]Define!I:I))</f>
-        <v>Resource</v>
+        <v>Alcana</v>
       </c>
       <c r="F5" s="1">
         <v>100</v>
@@ -1379,7 +1379,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1451,7 +1451,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1487,7 +1487,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1523,7 +1523,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1559,7 +1559,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1595,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/StageSymbol10.xlsx
+++ b/Assets/Data/StageSymbol10.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6620"/>
+    <workbookView windowWidth="19200" windowHeight="7070"/>
   </bookViews>
   <sheets>
     <sheet name="StageSymbols" sheetId="1" r:id="rId1"/>
@@ -76,9 +76,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -90,6 +90,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -97,14 +104,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -118,6 +118,98 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -126,53 +218,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -185,53 +232,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -242,187 +242,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -451,6 +451,35 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -462,6 +491,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -484,52 +528,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -541,145 +541,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -810,7 +810,7 @@
             <v>3</v>
           </cell>
           <cell r="J6" t="str">
-            <v>Recover</v>
+            <v>Event</v>
           </cell>
         </row>
         <row r="7">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="E10" s="1" t="str">
         <f>INDEX([1]Define!J:J,MATCH(D10,[1]Define!I:I))</f>
-        <v>Recover</v>
+        <v>Event</v>
       </c>
       <c r="F10" s="1">
         <v>100</v>

--- a/Assets/Data/StageSymbol10.xlsx
+++ b/Assets/Data/StageSymbol10.xlsx
@@ -77,8 +77,8 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -90,21 +90,39 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -118,6 +136,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -125,16 +166,52 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -148,22 +225,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -171,67 +232,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -242,31 +242,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -278,61 +338,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -344,85 +398,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -433,41 +433,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -480,17 +445,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -525,6 +486,45 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -541,7 +541,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -550,7 +550,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -559,127 +559,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/StageSymbol10.xlsx
+++ b/Assets/Data/StageSymbol10.xlsx
@@ -76,9 +76,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -90,7 +90,65 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -104,9 +162,56 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -122,114 +227,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -242,6 +242,132 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -254,37 +380,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -296,133 +422,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -439,49 +439,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -504,8 +463,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -527,12 +486,53 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -541,16 +541,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -559,127 +559,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
